--- a/resources/templates/standard/L1200-10.xlsx
+++ b/resources/templates/standard/L1200-10.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>{{companyName}} 협력회사 대여자산 관리대장</t>
   </si>
@@ -723,11 +726,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -795,7 +800,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="4"/>
@@ -813,78 +818,78 @@
       <c r="O4" s="6"/>
       <c r="P4" s="8"/>
       <c r="Q4" s="9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R4" s="9"/>
       <c r="S4" s="10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" s="10"/>
       <c r="U4" s="10"/>
     </row>
     <row r="5" ht="39.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R5" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S5" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U5" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="24.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
